--- a/backend/data/financials_by_company/0183.HK.xlsx
+++ b/backend/data/financials_by_company/0183.HK.xlsx
@@ -3719,182 +3719,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3997,28 +3997,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="V2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.145</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.143</v>
-      </c>
       <c r="X2" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.145</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.143</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0.145</v>
+        <v>0.151</v>
       </c>
       <c r="AC2" t="n">
         <v>1543968000</v>
@@ -4027,22 +4027,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.303</v>
+        <v>0.297</v>
       </c>
       <c r="AF2" t="n">
-        <v>133600</v>
+        <v>152000</v>
       </c>
       <c r="AG2" t="n">
-        <v>133600</v>
+        <v>152000</v>
       </c>
       <c r="AH2" t="n">
-        <v>50386</v>
+        <v>50137</v>
       </c>
       <c r="AI2" t="n">
-        <v>13600</v>
+        <v>58560</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13600</v>
+        <v>58560</v>
       </c>
       <c r="AK2" t="n">
         <v>0.144</v>
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>81068504</v>
+        <v>85603792</v>
       </c>
       <c r="AP2" t="n">
-        <v>84469972</v>
+        <v>85036884</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.131</v>
@@ -4075,13 +4075,13 @@
         <v>0.016</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.0829493</v>
+        <v>1.1435337</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.15066</v>
+        <v>0.15154</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.164785</v>
+        <v>0.163465</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>197016496</v>
+        <v>201551792</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.65402</v>
@@ -4122,7 +4122,7 @@
         <v>2.281</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.06269181</v>
+        <v>0.066199034</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -4148,16 +4148,16 @@
         <v>1620086400</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.632</v>
+        <v>2.692</v>
       </c>
       <c r="BS2" t="n">
-        <v>-27.178</v>
+        <v>-27.804</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.40399998</v>
+        <v>-0.49333334</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BV2" t="n">
         <v>0.018</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.143</v>
+        <v>0.151</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4272,138 +4272,138 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.6578961</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
           <t>WINFULL GP</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Winfull Group Holdings Limited</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1021944600000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.001000002</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.145 - 0.151</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>50137</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.019999996</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.15267172</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.131 - 0.325</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.174</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.5353846</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-49.333336</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1740405466</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1740405466</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>-0.09</v>
       </c>
-      <c r="DE2" t="n">
-        <v>-0.0076599866</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.05084287</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.021784991</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.13220252</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="EB2" t="n">
+        <v>-0.0005400032</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.0035634367</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.012465</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.07625485999999999</v>
+      </c>
+      <c r="EF2" t="n">
         <v>15</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="EG2" t="n">
         <v>15</v>
       </c>
-      <c r="DK2" t="n">
-        <v>1782112727</v>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>1783061508</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>finmb_7658032</t>
         </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-4.0268435</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1021944600000</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0059999973</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.143 - 0.145</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>50386</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.012000009</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.09160313</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.131 - 0.325</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.18199998</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.55999994</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-40.399998</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1740405466</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1740405466</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
